--- a/artfynd/A 8102-2024 artfynd.xlsx
+++ b/artfynd/A 8102-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>108533400</v>
       </c>
       <c r="B2" t="n">
-        <v>56315</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57903</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>393809.7262735458</v>
+        <v>393809</v>
       </c>
       <c r="R2" t="n">
-        <v>6295599.66644758</v>
+        <v>6295600</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -752,19 +747,9 @@
           <t>2023-03-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-03-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,6 +773,218 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>4767977</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99803</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222322</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ängsstarr</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Carex hostiana</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Brännebacka, Hl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>393770</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6295447</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Breared</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>1985-08-08</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1985-08-08</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Kärr</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Kjell Georgson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Kjell Georgson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Flora Halland</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4789788</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99879</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222361</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Loppstarr</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carex pulicaris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Brännebacka, Hl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>393770</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6295447</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Breared</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1985-08-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1985-08-08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Kärr</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kjell Georgson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kjell Georgson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Flora Halland</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8102-2024 artfynd.xlsx
+++ b/artfynd/A 8102-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108533400</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
           <t>Flora Halland</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4767977</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,8 +1000,18 @@
           <t>Flora Halland</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4789788</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>